--- a/labspreadsheet/production/local_input/LabSamples2026.xlsx
+++ b/labspreadsheet/production/local_input/LabSamples2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298228AE-EBBE-4361-BC22-E4E44E02EE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E048F1D8-3375-42AC-B1F7-77794E6D5A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-225" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="288">
   <si>
     <t>dropdown</t>
   </si>
@@ -866,6 +866,36 @@
   </si>
   <si>
     <t>SR, FK, JW, AS</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>Ron Rüegg</t>
+  </si>
+  <si>
+    <t>FK, RR</t>
+  </si>
+  <si>
+    <t>SR, RR</t>
+  </si>
+  <si>
+    <t>SR, FK, RR</t>
+  </si>
+  <si>
+    <t>chiavema</t>
+  </si>
+  <si>
+    <t>Matteo Chiavegato</t>
+  </si>
+  <si>
+    <t>waldnela</t>
+  </si>
+  <si>
+    <t>Laura Waldner</t>
+  </si>
+  <si>
+    <t>rueeggro</t>
   </si>
 </sst>
 </file>
@@ -1202,8 +1232,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -1615,31 +1648,31 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" t="s">
+        <v>283</v>
+      </c>
+      <c r="D30" t="s">
+        <v>284</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>34</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>34</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>35</v>
-      </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" t="s">
-        <v>38</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1647,13 +1680,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -1661,13 +1694,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
@@ -1675,13 +1708,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -1689,13 +1722,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -1703,13 +1736,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D36" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1717,60 +1750,58 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D37" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B38" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" t="s">
+        <v>251</v>
+      </c>
+      <c r="D38" t="s">
+        <v>252</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>285</v>
+      </c>
+      <c r="C39" t="s">
+        <v>285</v>
+      </c>
+      <c r="D39" t="s">
+        <v>286</v>
+      </c>
+      <c r="E39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>46</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>46</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" t="s">
         <v>47</v>
-      </c>
-      <c r="E38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" t="s">
-        <v>52</v>
       </c>
       <c r="E40" t="s">
         <v>48</v>
@@ -1779,13 +1810,13 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
@@ -1794,13 +1825,13 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" t="s">
-        <v>253</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>253</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>254</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
         <v>48</v>
@@ -1809,64 +1840,94 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A44" s="1"/>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>253</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>253</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>254</v>
       </c>
       <c r="E44" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="E45" t="s">
-        <v>258</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B48" t="s">
         <v>62</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C48" t="s">
         <v>62</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>63</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E48" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1877,8 +1938,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -1906,76 +1970,49 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B6" t="s">
         <v>68</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -1983,27 +2020,30 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>279</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -2011,13 +2051,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>79</v>
@@ -2025,13 +2065,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -2039,27 +2079,27 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -2067,27 +2107,27 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -2095,59 +2135,55 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>5</v>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>107</v>
-      </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -2155,69 +2191,73 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -2225,13 +2265,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -2239,13 +2279,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -2253,125 +2293,125 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
@@ -2379,69 +2419,69 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
         <v>5</v>
@@ -2449,13 +2489,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
         <v>5</v>
@@ -2463,13 +2503,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
         <v>137</v>
@@ -2477,27 +2517,27 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
         <v>5</v>
@@ -2505,385 +2545,441 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" t="s">
+        <v>169</v>
+      </c>
+      <c r="D49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>175</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C52" t="s">
         <v>175</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D52" t="s">
         <v>176</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>177</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C53" t="s">
         <v>177</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D53" t="s">
         <v>178</v>
       </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>179</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C54" t="s">
         <v>179</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D54" t="s">
         <v>180</v>
       </c>
-      <c r="E50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>181</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C55" t="s">
         <v>182</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D55" t="s">
         <v>183</v>
-      </c>
-      <c r="E51" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>184</v>
-      </c>
-      <c r="C52" t="s">
-        <v>185</v>
-      </c>
-      <c r="D52" t="s">
-        <v>186</v>
-      </c>
-      <c r="E52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" t="s">
-        <v>82</v>
-      </c>
-      <c r="D54" t="s">
-        <v>83</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>264</v>
-      </c>
-      <c r="C55" t="s">
-        <v>265</v>
-      </c>
-      <c r="D55" t="s">
-        <v>266</v>
       </c>
       <c r="E55" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
-        <v>267</v>
+        <v>185</v>
       </c>
       <c r="D56" t="s">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" t="s">
+        <v>266</v>
+      </c>
+      <c r="E59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" t="s">
+        <v>267</v>
+      </c>
+      <c r="D60" t="s">
+        <v>268</v>
+      </c>
+      <c r="E60" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>66</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
         <v>277</v>
       </c>
     </row>
